--- a/2_Funds_parser/Input/list_of_funds.xlsx
+++ b/2_Funds_parser/Input/list_of_funds.xlsx
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Boxer Capital, LLC</t>
+          <t>Boxer Capital Management, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0001465837</t>
+          <t>0002018299</t>
         </is>
       </c>
     </row>
